--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -26,8 +26,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+玩家中奖倍数触发对应掉落，区间为左闭右开</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -41,16 +73,31 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>DropType</t>
+  </si>
+  <si>
+    <t>1_999999</t>
   </si>
   <si>
     <t>消耗能量时，触发中奖</t>
   </si>
   <si>
+    <t>5_10</t>
+  </si>
+  <si>
     <t>消耗能量时，触发5-10倍中奖</t>
   </si>
   <si>
+    <t>10_20</t>
+  </si>
+  <si>
     <t>消耗能量时，触发10-20倍中奖</t>
+  </si>
+  <si>
+    <t>20_30</t>
   </si>
   <si>
     <t>消耗能量时，触发20-30倍中奖</t>
@@ -66,7 +113,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +270,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1207,12 +1265,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
-    <col min="3" max="3" width="28.375" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:3">
@@ -1231,70 +1289,137 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
     </row>
     <row r="5" ht="16.5" spans="1:3">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:3">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:3">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
-      <c r="B7" s="1">
-        <v>3</v>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:3">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
-      <c r="B8" s="1">
-        <v>4</v>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:3">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:3">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:3">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:3">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:3">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:3">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:3">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:3">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" ht="16.5" spans="2:2">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" ht="16.5" spans="2:2">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" ht="16.5" spans="2:2">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" ht="16.5" spans="2:2">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" ht="16.5" spans="2:2">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" ht="16.5" spans="2:2">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" ht="16.5" spans="2:2">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" ht="16.5" spans="2:2">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" ht="16.5" spans="2:2">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" ht="16.5" spans="2:2">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" ht="16.5" spans="2:2">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28" ht="16.5" spans="2:2">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" ht="16.5" spans="2:2">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" ht="16.5" spans="2:2">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" ht="16.5" spans="2:2">
+      <c r="B31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -85,22 +85,22 @@
     <t>消耗能量时，触发中奖</t>
   </si>
   <si>
-    <t>5_10</t>
-  </si>
-  <si>
-    <t>消耗能量时，触发5-10倍中奖</t>
-  </si>
-  <si>
     <t>10_20</t>
   </si>
   <si>
-    <t>消耗能量时，触发10-20倍中奖</t>
+    <t>消耗能量时，触发10-20倍大奖</t>
   </si>
   <si>
-    <t>20_30</t>
+    <t>25_999999</t>
   </si>
   <si>
-    <t>消耗能量时，触发20-30倍中奖</t>
+    <t>消耗能量时，触发25倍及以上大奖</t>
+  </si>
+  <si>
+    <t>20_999999</t>
+  </si>
+  <si>
+    <t>消耗能量时，触发20倍及以上大奖</t>
   </si>
 </sst>
 </file>
@@ -1349,6 +1349,7 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:3">
+      <c r="A9" s="1"/>
       <c r="B9" s="1"/>
     </row>
     <row r="10" ht="16.5" spans="1:3">

--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>消耗能量时，触发20倍及以上大奖</t>
+  </si>
+  <si>
+    <t>50_999999</t>
+  </si>
+  <si>
+    <t>消耗能量时，触发50倍及以上大奖</t>
   </si>
 </sst>
 </file>
@@ -1349,8 +1355,15 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" ht="16.5" spans="1:3">
       <c r="B10" s="1"/>

--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>消耗能量时，触发50倍及以上大奖</t>
+  </si>
+  <si>
+    <t>5_999999</t>
+  </si>
+  <si>
+    <t>消耗能量时，触发5倍及以上大奖</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1372,15 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:3">
-      <c r="B10" s="1"/>
+      <c r="A10" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="B11" s="1"/>

--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -3,11 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="dropType" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +38,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,23 +65,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>允许执行的模式</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>掉落方式</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>ExecutionMode</t>
+  </si>
+  <si>
     <t>DropType</t>
   </si>
   <si>
@@ -113,6 +125,18 @@
   </si>
   <si>
     <t>消耗能量时，触发5倍及以上大奖</t>
+  </si>
+  <si>
+    <t>50_100</t>
+  </si>
+  <si>
+    <t>在此模式下根据玩家中奖的倍数触发对应掉落</t>
+  </si>
+  <si>
+    <t>1是增加允许执行的模式</t>
+  </si>
+  <si>
+    <t>2是在特殊模式下触发特殊掉落，掉落根据倍数特殊模式下的总倍数控制，在特殊模式结束时触发</t>
   </si>
 </sst>
 </file>
@@ -1277,15 +1301,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="25.25" customWidth="1"/>
+    <col min="1" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:3">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,159 +1319,232 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:3">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:3">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:3">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:3">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:3">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:3">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:3">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:3">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:3">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:3">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:3">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" ht="16.5" spans="2:2">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" ht="16.5" spans="2:2">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" ht="16.5" spans="2:2">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" ht="16.5" spans="2:2">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" ht="16.5" spans="2:2">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" ht="16.5" spans="2:2">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" ht="16.5" spans="2:2">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" ht="16.5" spans="2:2">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" ht="16.5" spans="2:2">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" ht="16.5" spans="2:2">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" ht="16.5" spans="2:2">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" ht="16.5" spans="2:2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" ht="16.5" spans="2:2">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" ht="16.5" spans="2:2">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" ht="16.5" spans="2:2">
-      <c r="B31" s="1"/>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:5">
+      <c r="A11" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:5">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:5">
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:5">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:5">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:5">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" ht="16.5" spans="4:4">
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" ht="16.5" spans="4:4">
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" ht="16.5" spans="4:4">
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" ht="16.5" spans="4:4">
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" ht="16.5" spans="4:4">
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" ht="16.5" spans="4:4">
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" ht="16.5" spans="4:4">
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" ht="16.5" spans="4:4">
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" ht="16.5" spans="4:4">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" ht="16.5" spans="4:4">
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" ht="16.5" spans="4:4">
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" ht="16.5" spans="4:4">
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" ht="16.5" spans="4:4">
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" ht="16.5" spans="4:4">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" ht="16.5" spans="4:4">
+      <c r="D31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/dropType.xlsx
+++ b/hall/resources/sample/dropType.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropType" sheetId="1" r:id="rId1"/>
@@ -1331,7 +1331,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
